--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\GitHub\Diploma-Thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36EE611E-1D84-4484-ACC3-3DF129F13123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490410E0-6A50-4627-A0BD-0D8BAD959300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3831FB66-E462-4D2F-BE31-1EB6A20DBCB8}"/>
   </bookViews>
@@ -514,6 +514,7 @@
     <col min="9" max="9" width="10.140625" customWidth="1"/>
     <col min="10" max="10" width="26.28515625" customWidth="1"/>
     <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="16" max="16" width="17.28515625" customWidth="1"/>
     <col min="17" max="17" width="26.140625" customWidth="1"/>
     <col min="18" max="18" width="11.42578125" customWidth="1"/>
     <col min="19" max="19" width="20.42578125" customWidth="1"/>
@@ -583,15 +584,15 @@
         <v>3.1059999999999999</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G11" si="0">ABS(E4-$B$3)/$B$3</f>
+        <f t="shared" ref="G4:G12" si="0">ABS(E4-$B$3)/$B$3</f>
         <v>1.0901883052527277E-2</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H11" si="1">ABS(F4-$C$3)/$C$3</f>
+        <f t="shared" ref="H4:H12" si="1">ABS(F4-$C$3)/$C$3</f>
         <v>8.3963860422054046E-3</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J11" si="2">MAX(G4:H4)*100</f>
+        <f t="shared" ref="J4:J12" si="2">MAX(G4:H4)*100</f>
         <v>1.0901883052527277</v>
       </c>
       <c r="P4" t="s">
@@ -780,6 +781,24 @@
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="F12">
+        <v>3.15</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>1.3324523730866499E-2</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>5.650799731826469E-3</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="2"/>
+        <v>1.33245237308665</v>
+      </c>
       <c r="P12" t="s">
         <v>4</v>
       </c>
